--- a/data/RT2/Current_24_RT2.xlsx
+++ b/data/RT2/Current_24_RT2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Consec. no.</t>
   </si>
@@ -103,36 +103,39 @@
     <t>Södergående - Sundbyberg</t>
   </si>
   <si>
+    <t>Sub</t>
+  </si>
+  <si>
+    <t>Huv</t>
+  </si>
+  <si>
+    <t>TmÖ</t>
+  </si>
+  <si>
+    <t>Sod</t>
+  </si>
+  <si>
+    <t>Sci</t>
+  </si>
+  <si>
+    <t>Sst</t>
+  </si>
+  <si>
+    <t>Åbe</t>
+  </si>
+  <si>
     <t>Äs</t>
   </si>
   <si>
     <t>-1 23:59:57</t>
   </si>
   <si>
-    <t>Åbe</t>
-  </si>
-  <si>
-    <t>Sst</t>
-  </si>
-  <si>
-    <t>Sci</t>
-  </si>
-  <si>
-    <t>Sod</t>
-  </si>
-  <si>
-    <t>TmÖ</t>
-  </si>
-  <si>
-    <t>Huv</t>
-  </si>
-  <si>
-    <t>Sub</t>
-  </si>
-  <si>
     <t>Södergående - Solna</t>
   </si>
   <si>
+    <t>So</t>
+  </si>
+  <si>
     <t>Norrgående - Älvsjö - Sundbyberg</t>
   </si>
   <si>
@@ -140,6 +143,9 @@
   </si>
   <si>
     <t>Norrgående - Älvsjö - Solna</t>
+  </si>
+  <si>
+    <t>-1 23:59:56</t>
   </si>
   <si>
     <t>Alla</t>
@@ -601,7 +607,7 @@
     </row>
     <row r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -681,7 +687,7 @@
     </row>
     <row r="3" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>27</v>
@@ -693,22 +699,22 @@
         <v>29</v>
       </c>
       <c r="E3" s="8">
-        <v>0.00162037037037037</v>
+        <v>0.000983796296296296</v>
       </c>
       <c r="F3" s="8">
-        <v>0.00158564814814815</v>
+        <v>0.00099537037037037</v>
       </c>
       <c r="G3" s="9">
-        <v>79.3061224489796</v>
+        <v>92.4081632653061</v>
       </c>
       <c r="H3" s="9">
-        <v>79.8571428571429</v>
+        <v>92.3265306122449</v>
       </c>
       <c r="I3" s="9">
-        <v>44.26</v>
+        <v>48.23</v>
       </c>
       <c r="J3" s="9">
-        <v>42.9</v>
+        <v>45.51</v>
       </c>
       <c r="K3" s="9">
         <v>49</v>
@@ -719,11 +725,11 @@
       <c r="M3" s="9">
         <v>49</v>
       </c>
-      <c r="N3" s="10" t="s">
-        <v>30</v>
+      <c r="N3" s="8">
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="O3" s="8">
-        <v>0</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P3" s="8">
         <v>0.000185185185185185</v>
@@ -741,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="U3" s="8">
-        <v>0</v>
+        <v>0.000972222222222222</v>
       </c>
       <c r="V3" s="9">
         <v>0</v>
       </c>
       <c r="W3" s="9">
-        <v>43.27</v>
+        <v>44.32</v>
       </c>
       <c r="X3" s="9">
         <v>0</v>
@@ -756,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="9">
-        <v>0</v>
+        <v>48.2</v>
       </c>
       <c r="AA3" s="9">
         <v>0</v>
@@ -764,7 +770,7 @@
     </row>
     <row r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>27</v>
@@ -773,25 +779,25 @@
         <v>28</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" s="8">
-        <v>0.00165509259259259</v>
+        <v>0.00100694444444444</v>
       </c>
       <c r="F4" s="8">
-        <v>0.00166666666666667</v>
+        <v>0.00100694444444444</v>
       </c>
       <c r="G4" s="9">
-        <v>78.6326530612245</v>
+        <v>92.3265306122449</v>
       </c>
       <c r="H4" s="9">
-        <v>78.530612244898</v>
+        <v>92.3265306122449</v>
       </c>
       <c r="I4" s="9">
-        <v>44.32</v>
+        <v>45.52</v>
       </c>
       <c r="J4" s="9">
-        <v>44.37</v>
+        <v>45.52</v>
       </c>
       <c r="K4" s="9">
         <v>49</v>
@@ -803,19 +809,19 @@
         <v>49</v>
       </c>
       <c r="N4" s="8">
-        <v>1.15740740740741e-005</v>
+        <v>0</v>
       </c>
       <c r="O4" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0</v>
       </c>
       <c r="P4" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
       </c>
       <c r="R4" s="8">
-        <v>0.000173611111111111</v>
+        <v>0</v>
       </c>
       <c r="S4" s="8">
         <v>0</v>
@@ -830,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="W4" s="9">
-        <v>43.12</v>
+        <v>0</v>
       </c>
       <c r="X4" s="9">
         <v>0</v>
@@ -847,7 +853,7 @@
     </row>
     <row r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>27</v>
@@ -856,25 +862,25 @@
         <v>28</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="8">
-        <v>0.00149305555555556</v>
+        <v>0.0009375</v>
       </c>
       <c r="F5" s="8">
-        <v>0.00150462962962963</v>
+        <v>0.000949074074074074</v>
       </c>
       <c r="G5" s="9">
-        <v>81.7959183673469</v>
+        <v>92.4285714285714</v>
       </c>
       <c r="H5" s="9">
-        <v>81.469387755102</v>
+        <v>92.3673469387755</v>
       </c>
       <c r="I5" s="9">
-        <v>49</v>
+        <v>45.97</v>
       </c>
       <c r="J5" s="9">
-        <v>42.12</v>
+        <v>45.97</v>
       </c>
       <c r="K5" s="9">
         <v>49</v>
@@ -886,19 +892,19 @@
         <v>49</v>
       </c>
       <c r="N5" s="8">
-        <v>2.31481481481481e-005</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0</v>
       </c>
       <c r="P5" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="8">
         <v>0</v>
       </c>
       <c r="R5" s="8">
-        <v>0.000162037037037037</v>
+        <v>0</v>
       </c>
       <c r="S5" s="8">
         <v>0</v>
@@ -913,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="9">
-        <v>41.11</v>
+        <v>0</v>
       </c>
       <c r="X5" s="9">
         <v>0</v>
@@ -930,7 +936,7 @@
     </row>
     <row r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>27</v>
@@ -939,25 +945,25 @@
         <v>28</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="8">
-        <v>0.00122685185185185</v>
+        <v>0.00163194444444444</v>
       </c>
       <c r="F6" s="8">
-        <v>0.00130787037037037</v>
+        <v>0.00175925925925926</v>
       </c>
       <c r="G6" s="9">
-        <v>85.5510204081633</v>
+        <v>84.530612244898</v>
       </c>
       <c r="H6" s="9">
-        <v>84.5102040816327</v>
+        <v>82.6938775510204</v>
       </c>
       <c r="I6" s="9">
-        <v>30.01</v>
+        <v>49</v>
       </c>
       <c r="J6" s="9">
-        <v>32.17</v>
+        <v>49</v>
       </c>
       <c r="K6" s="9">
         <v>49</v>
@@ -969,19 +975,19 @@
         <v>49</v>
       </c>
       <c r="N6" s="8">
-        <v>0.000162037037037037</v>
+        <v>0.000115740740740741</v>
       </c>
       <c r="O6" s="8">
-        <v>0.00025462962962963</v>
+        <v>0.000138888888888889</v>
       </c>
       <c r="P6" s="8">
-        <v>0.000648148148148148</v>
+        <v>0.000150462962962963</v>
       </c>
       <c r="Q6" s="8">
         <v>0</v>
       </c>
       <c r="R6" s="8">
-        <v>0.000358796296296296</v>
+        <v>0.000266203703703704</v>
       </c>
       <c r="S6" s="8">
         <v>0</v>
@@ -996,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="9">
-        <v>31.61</v>
+        <v>48.22</v>
       </c>
       <c r="X6" s="9">
         <v>0</v>
@@ -1013,7 +1019,7 @@
     </row>
     <row r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>27</v>
@@ -1022,25 +1028,25 @@
         <v>28</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="8">
-        <v>0.00163194444444444</v>
+        <v>0.00122685185185185</v>
       </c>
       <c r="F7" s="8">
-        <v>0.00175925925925926</v>
+        <v>0.00130787037037037</v>
       </c>
       <c r="G7" s="9">
-        <v>84.530612244898</v>
+        <v>85.5510204081633</v>
       </c>
       <c r="H7" s="9">
-        <v>82.6938775510204</v>
+        <v>84.5102040816327</v>
       </c>
       <c r="I7" s="9">
-        <v>49</v>
+        <v>30.01</v>
       </c>
       <c r="J7" s="9">
-        <v>49</v>
+        <v>32.17</v>
       </c>
       <c r="K7" s="9">
         <v>49</v>
@@ -1052,19 +1058,19 @@
         <v>49</v>
       </c>
       <c r="N7" s="8">
-        <v>0.000115740740740741</v>
+        <v>0.000162037037037037</v>
       </c>
       <c r="O7" s="8">
-        <v>0.000138888888888889</v>
+        <v>0.00025462962962963</v>
       </c>
       <c r="P7" s="8">
-        <v>0.000150462962962963</v>
+        <v>0.000648148148148148</v>
       </c>
       <c r="Q7" s="8">
         <v>0</v>
       </c>
       <c r="R7" s="8">
-        <v>0.000266203703703704</v>
+        <v>0.000358796296296296</v>
       </c>
       <c r="S7" s="8">
         <v>0</v>
@@ -1079,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="9">
-        <v>48.22</v>
+        <v>31.61</v>
       </c>
       <c r="X7" s="9">
         <v>0</v>
@@ -1096,7 +1102,7 @@
     </row>
     <row r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>27</v>
@@ -1105,25 +1111,25 @@
         <v>28</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="8">
-        <v>0.0009375</v>
+        <v>0.00149305555555556</v>
       </c>
       <c r="F8" s="8">
-        <v>0.000949074074074074</v>
+        <v>0.00150462962962963</v>
       </c>
       <c r="G8" s="9">
-        <v>92.4285714285714</v>
+        <v>81.7959183673469</v>
       </c>
       <c r="H8" s="9">
-        <v>92.3673469387755</v>
+        <v>81.469387755102</v>
       </c>
       <c r="I8" s="9">
-        <v>45.97</v>
+        <v>49</v>
       </c>
       <c r="J8" s="9">
-        <v>45.97</v>
+        <v>42.12</v>
       </c>
       <c r="K8" s="9">
         <v>49</v>
@@ -1135,19 +1141,19 @@
         <v>49</v>
       </c>
       <c r="N8" s="8">
-        <v>0</v>
+        <v>2.31481481481481e-005</v>
       </c>
       <c r="O8" s="8">
-        <v>0</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P8" s="8">
-        <v>0</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="Q8" s="8">
         <v>0</v>
       </c>
       <c r="R8" s="8">
-        <v>0</v>
+        <v>0.000162037037037037</v>
       </c>
       <c r="S8" s="8">
         <v>0</v>
@@ -1162,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="9">
-        <v>0</v>
+        <v>41.11</v>
       </c>
       <c r="X8" s="9">
         <v>0</v>
@@ -1179,7 +1185,7 @@
     </row>
     <row r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>27</v>
@@ -1188,25 +1194,25 @@
         <v>28</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="8">
-        <v>0.00100694444444444</v>
+        <v>0.00165509259259259</v>
       </c>
       <c r="F9" s="8">
-        <v>0.00100694444444444</v>
+        <v>0.00166666666666667</v>
       </c>
       <c r="G9" s="9">
-        <v>92.3265306122449</v>
+        <v>78.6326530612245</v>
       </c>
       <c r="H9" s="9">
-        <v>92.3265306122449</v>
+        <v>78.530612244898</v>
       </c>
       <c r="I9" s="9">
-        <v>45.52</v>
+        <v>44.32</v>
       </c>
       <c r="J9" s="9">
-        <v>45.52</v>
+        <v>44.37</v>
       </c>
       <c r="K9" s="9">
         <v>49</v>
@@ -1218,19 +1224,19 @@
         <v>49</v>
       </c>
       <c r="N9" s="8">
-        <v>0</v>
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="O9" s="8">
-        <v>0</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P9" s="8">
-        <v>0</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="Q9" s="8">
         <v>0</v>
       </c>
       <c r="R9" s="8">
-        <v>0</v>
+        <v>0.000173611111111111</v>
       </c>
       <c r="S9" s="8">
         <v>0</v>
@@ -1245,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="W9" s="9">
-        <v>0</v>
+        <v>43.12</v>
       </c>
       <c r="X9" s="9">
         <v>0</v>
@@ -1262,7 +1268,7 @@
     </row>
     <row r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>27</v>
@@ -1271,40 +1277,40 @@
         <v>28</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.00162037037037037</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.00158564814814815</v>
+      </c>
+      <c r="G10" s="9">
+        <v>79.3061224489796</v>
+      </c>
+      <c r="H10" s="9">
+        <v>79.8571428571429</v>
+      </c>
+      <c r="I10" s="9">
+        <v>44.26</v>
+      </c>
+      <c r="J10" s="9">
+        <v>42.9</v>
+      </c>
+      <c r="K10" s="9">
+        <v>49</v>
+      </c>
+      <c r="L10" s="9">
+        <v>49</v>
+      </c>
+      <c r="M10" s="9">
+        <v>49</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.000983796296296296</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.00099537037037037</v>
-      </c>
-      <c r="G10" s="9">
-        <v>92.4081632653061</v>
-      </c>
-      <c r="H10" s="9">
-        <v>92.3265306122449</v>
-      </c>
-      <c r="I10" s="9">
-        <v>48.23</v>
-      </c>
-      <c r="J10" s="9">
-        <v>45.51</v>
-      </c>
-      <c r="K10" s="9">
-        <v>49</v>
-      </c>
-      <c r="L10" s="9">
-        <v>49</v>
-      </c>
-      <c r="M10" s="9">
-        <v>49</v>
-      </c>
-      <c r="N10" s="8">
-        <v>1.15740740740741e-005</v>
-      </c>
       <c r="O10" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0</v>
       </c>
       <c r="P10" s="8">
         <v>0.000185185185185185</v>
@@ -1322,13 +1328,13 @@
         <v>0</v>
       </c>
       <c r="U10" s="8">
-        <v>0.000972222222222222</v>
+        <v>0</v>
       </c>
       <c r="V10" s="9">
         <v>0</v>
       </c>
       <c r="W10" s="9">
-        <v>44.32</v>
+        <v>43.27</v>
       </c>
       <c r="X10" s="9">
         <v>0</v>
@@ -1337,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="9">
-        <v>48.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="9">
         <v>0</v>
@@ -1345,7 +1351,7 @@
     </row>
     <row r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>27</v>
@@ -1354,31 +1360,31 @@
         <v>38</v>
       </c>
       <c r="E11" s="4">
-        <v>0.00186342592592593</v>
+        <v>0.00180555555555556</v>
       </c>
       <c r="F11" s="4">
-        <v>0.00189814814814815</v>
+        <v>0.00184027777777778</v>
       </c>
       <c r="G11" s="5">
-        <v>77.530612244898</v>
+        <v>78.6588921282799</v>
       </c>
       <c r="H11" s="5">
-        <v>76.8299319727891</v>
+        <v>78.0379008746356</v>
       </c>
       <c r="I11" s="5">
-        <v>266.6</v>
+        <v>314.96</v>
       </c>
       <c r="J11" s="5">
-        <v>262.07</v>
+        <v>308.11</v>
       </c>
       <c r="K11" s="5">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="L11" s="5">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="M11" s="5">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="N11" s="4">
         <v>4.62962962962963e-005</v>
@@ -1387,7 +1393,7 @@
         <v>8.10185185185185e-005</v>
       </c>
       <c r="P11" s="4">
-        <v>0.000231481481481481</v>
+        <v>0.000219907407407407</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -1402,13 +1408,13 @@
         <v>0</v>
       </c>
       <c r="U11" s="4">
-        <v>0</v>
+        <v>0.000208333333333333</v>
       </c>
       <c r="V11" s="5">
         <v>0</v>
       </c>
       <c r="W11" s="5">
-        <v>212.15</v>
+        <v>256.9</v>
       </c>
       <c r="X11" s="5">
         <v>0</v>
@@ -1417,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="5">
-        <v>0</v>
+        <v>48.32</v>
       </c>
       <c r="AA11" s="5">
         <v>4.68</v>
@@ -1425,7 +1431,7 @@
     </row>
     <row r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>27</v>
@@ -1434,25 +1440,25 @@
         <v>38</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E12" s="8">
-        <v>0.00202546296296296</v>
+        <v>0.00144675925925926</v>
       </c>
       <c r="F12" s="8">
-        <v>0.00199074074074074</v>
+        <v>0.00146990740740741</v>
       </c>
       <c r="G12" s="9">
-        <v>73.9795918367347</v>
+        <v>85.4285714285714</v>
       </c>
       <c r="H12" s="9">
-        <v>74.3469387755102</v>
+        <v>85.2857142857143</v>
       </c>
       <c r="I12" s="9">
-        <v>44.88</v>
+        <v>48.36</v>
       </c>
       <c r="J12" s="9">
-        <v>43.83</v>
+        <v>46.04</v>
       </c>
       <c r="K12" s="9">
         <v>49</v>
@@ -1463,11 +1469,11 @@
       <c r="M12" s="9">
         <v>49</v>
       </c>
-      <c r="N12" s="10" t="s">
-        <v>30</v>
+      <c r="N12" s="8">
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="O12" s="8">
-        <v>0</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P12" s="8">
         <v>0.000185185185185185</v>
@@ -1476,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="8">
-        <v>0.000173611111111111</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="S12" s="8">
         <v>0</v>
@@ -1485,13 +1491,13 @@
         <v>0</v>
       </c>
       <c r="U12" s="8">
-        <v>0</v>
+        <v>0.00142361111111111</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
       </c>
       <c r="W12" s="9">
-        <v>43.87</v>
+        <v>44.75</v>
       </c>
       <c r="X12" s="9">
         <v>0</v>
@@ -1500,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="9">
-        <v>0</v>
+        <v>48.32</v>
       </c>
       <c r="AA12" s="9">
         <v>0</v>
@@ -1508,7 +1514,7 @@
     </row>
     <row r="13" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>27</v>
@@ -1520,22 +1526,22 @@
         <v>31</v>
       </c>
       <c r="E13" s="8">
-        <v>0.00210648148148148</v>
+        <v>0.00141203703703704</v>
       </c>
       <c r="F13" s="8">
-        <v>0.00212962962962963</v>
+        <v>0.00142361111111111</v>
       </c>
       <c r="G13" s="9">
-        <v>72.6530612244898</v>
+        <v>85.6122448979592</v>
       </c>
       <c r="H13" s="9">
-        <v>72.4489795918367</v>
+        <v>85.0612244897959</v>
       </c>
       <c r="I13" s="9">
-        <v>45.05</v>
+        <v>46.32</v>
       </c>
       <c r="J13" s="9">
-        <v>45.25</v>
+        <v>46.32</v>
       </c>
       <c r="K13" s="9">
         <v>49</v>
@@ -1550,16 +1556,16 @@
         <v>1.15740740740741e-005</v>
       </c>
       <c r="O13" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="P13" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="8">
         <v>0</v>
       </c>
       <c r="R13" s="8">
-        <v>0.000173611111111111</v>
+        <v>0</v>
       </c>
       <c r="S13" s="8">
         <v>0</v>
@@ -1574,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="9">
-        <v>44.05</v>
+        <v>0</v>
       </c>
       <c r="X13" s="9">
         <v>0</v>
@@ -1591,7 +1597,7 @@
     </row>
     <row r="14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>27</v>
@@ -1603,22 +1609,22 @@
         <v>32</v>
       </c>
       <c r="E14" s="8">
-        <v>0.0019212962962963</v>
+        <v>0.00212962962962963</v>
       </c>
       <c r="F14" s="8">
-        <v>0.00194444444444444</v>
+        <v>0.00225694444444444</v>
       </c>
       <c r="G14" s="9">
-        <v>75.8775510204082</v>
+        <v>76.6326530612245</v>
       </c>
       <c r="H14" s="9">
-        <v>75.6122448979592</v>
+        <v>74.2448979591837</v>
       </c>
       <c r="I14" s="9">
         <v>49</v>
       </c>
       <c r="J14" s="9">
-        <v>43</v>
+        <v>48.98</v>
       </c>
       <c r="K14" s="9">
         <v>49</v>
@@ -1630,19 +1636,19 @@
         <v>49</v>
       </c>
       <c r="N14" s="8">
-        <v>2.31481481481481e-005</v>
+        <v>0.000127314814814815</v>
       </c>
       <c r="O14" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0.000138888888888889</v>
       </c>
       <c r="P14" s="8">
-        <v>0.000185185185185185</v>
+        <v>0.000150462962962963</v>
       </c>
       <c r="Q14" s="8">
         <v>0</v>
       </c>
       <c r="R14" s="8">
-        <v>0.000162037037037037</v>
+        <v>0.000277777777777778</v>
       </c>
       <c r="S14" s="8">
         <v>0</v>
@@ -1657,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="W14" s="9">
-        <v>41.97</v>
+        <v>48.33</v>
       </c>
       <c r="X14" s="9">
         <v>0</v>
@@ -1674,7 +1680,7 @@
     </row>
     <row r="15" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>27</v>
@@ -1757,7 +1763,7 @@
     </row>
     <row r="16" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>27</v>
@@ -1769,22 +1775,22 @@
         <v>34</v>
       </c>
       <c r="E16" s="8">
-        <v>0.00212962962962963</v>
+        <v>0.0019212962962963</v>
       </c>
       <c r="F16" s="8">
-        <v>0.00225694444444444</v>
+        <v>0.00194444444444444</v>
       </c>
       <c r="G16" s="9">
-        <v>76.6326530612245</v>
+        <v>75.8775510204082</v>
       </c>
       <c r="H16" s="9">
-        <v>74.2448979591837</v>
+        <v>75.6122448979592</v>
       </c>
       <c r="I16" s="9">
         <v>49</v>
       </c>
       <c r="J16" s="9">
-        <v>48.98</v>
+        <v>43</v>
       </c>
       <c r="K16" s="9">
         <v>49</v>
@@ -1796,19 +1802,19 @@
         <v>49</v>
       </c>
       <c r="N16" s="8">
-        <v>0.000127314814814815</v>
+        <v>2.31481481481481e-005</v>
       </c>
       <c r="O16" s="8">
-        <v>0.000138888888888889</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P16" s="8">
-        <v>0.000150462962962963</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="Q16" s="8">
         <v>0</v>
       </c>
       <c r="R16" s="8">
-        <v>0.000277777777777778</v>
+        <v>0.000162037037037037</v>
       </c>
       <c r="S16" s="8">
         <v>0</v>
@@ -1823,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="W16" s="9">
-        <v>48.33</v>
+        <v>41.97</v>
       </c>
       <c r="X16" s="9">
         <v>0</v>
@@ -1840,7 +1846,7 @@
     </row>
     <row r="17" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>27</v>
@@ -1852,22 +1858,22 @@
         <v>35</v>
       </c>
       <c r="E17" s="8">
-        <v>0.00141203703703704</v>
+        <v>0.00210648148148148</v>
       </c>
       <c r="F17" s="8">
-        <v>0.00142361111111111</v>
+        <v>0.00212962962962963</v>
       </c>
       <c r="G17" s="9">
-        <v>85.6122448979592</v>
+        <v>72.6530612244898</v>
       </c>
       <c r="H17" s="9">
-        <v>85.0612244897959</v>
+        <v>72.4489795918367</v>
       </c>
       <c r="I17" s="9">
-        <v>46.32</v>
+        <v>45.05</v>
       </c>
       <c r="J17" s="9">
-        <v>46.32</v>
+        <v>45.25</v>
       </c>
       <c r="K17" s="9">
         <v>49</v>
@@ -1882,16 +1888,16 @@
         <v>1.15740740740741e-005</v>
       </c>
       <c r="O17" s="8">
-        <v>1.15740740740741e-005</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P17" s="8">
-        <v>0</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="Q17" s="8">
         <v>0</v>
       </c>
       <c r="R17" s="8">
-        <v>0</v>
+        <v>0.000173611111111111</v>
       </c>
       <c r="S17" s="8">
         <v>0</v>
@@ -1906,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="9">
-        <v>0</v>
+        <v>44.05</v>
       </c>
       <c r="X17" s="9">
         <v>0</v>
@@ -1922,198 +1928,198 @@
       </c>
     </row>
     <row r="18" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>25</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="A18" s="6">
+        <v>28</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.00202546296296296</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.00199074074074074</v>
+      </c>
+      <c r="G18" s="9">
+        <v>73.9795918367347</v>
+      </c>
+      <c r="H18" s="9">
+        <v>74.3469387755102</v>
+      </c>
+      <c r="I18" s="9">
+        <v>44.88</v>
+      </c>
+      <c r="J18" s="9">
+        <v>43.83</v>
+      </c>
+      <c r="K18" s="9">
+        <v>49</v>
+      </c>
+      <c r="L18" s="9">
+        <v>49</v>
+      </c>
+      <c r="M18" s="9">
+        <v>49</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0.000173611111111111</v>
+      </c>
+      <c r="S18" s="8">
+        <v>0</v>
+      </c>
+      <c r="T18" s="8">
+        <v>0</v>
+      </c>
+      <c r="U18" s="8">
+        <v>0</v>
+      </c>
+      <c r="V18" s="9">
+        <v>0</v>
+      </c>
+      <c r="W18" s="9">
+        <v>43.87</v>
+      </c>
+      <c r="X18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>27</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="4">
         <v>0.00131944444444444</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F19" s="4">
         <v>0.00135416666666667</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G19" s="5">
         <v>85.0739795918367</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H19" s="5">
         <v>84.5357142857143</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I19" s="5">
         <v>347.01</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J19" s="5">
         <v>344.86</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K19" s="5">
         <v>392</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L19" s="5">
         <v>392</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M19" s="5">
         <v>392</v>
       </c>
-      <c r="N18" s="4">
+      <c r="N19" s="4">
         <v>3.47222222222222e-005</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O19" s="4">
         <v>6.94444444444444e-005</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P19" s="4">
         <v>0.000196759259259259</v>
       </c>
-      <c r="Q18" s="4">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4">
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
         <v>0.000162037037037037</v>
       </c>
-      <c r="S18" s="4">
-        <v>0</v>
-      </c>
-      <c r="T18" s="4">
-        <v>0</v>
-      </c>
-      <c r="U18" s="4">
+      <c r="S19" s="4">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
         <v>0.000127314814814815</v>
       </c>
-      <c r="V18" s="5">
-        <v>0</v>
-      </c>
-      <c r="W18" s="5">
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
         <v>253.92</v>
       </c>
-      <c r="X18" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="5">
+      <c r="X19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
         <v>48.25</v>
       </c>
-      <c r="AA18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>24</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.00099537037037037</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0.00101851851851852</v>
-      </c>
-      <c r="G19" s="9">
-        <v>91.3673469387755</v>
-      </c>
-      <c r="H19" s="9">
-        <v>91.2448979591837</v>
-      </c>
-      <c r="I19" s="9">
-        <v>48.27</v>
-      </c>
-      <c r="J19" s="9">
-        <v>45.45</v>
-      </c>
-      <c r="K19" s="9">
-        <v>49</v>
-      </c>
-      <c r="L19" s="9">
-        <v>49</v>
-      </c>
-      <c r="M19" s="9">
-        <v>49</v>
-      </c>
-      <c r="N19" s="8">
-        <v>1.15740740740741e-005</v>
-      </c>
-      <c r="O19" s="8">
-        <v>5.78703703703704e-005</v>
-      </c>
-      <c r="P19" s="8">
-        <v>0.000185185185185185</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8">
-        <v>0.000173611111111111</v>
-      </c>
-      <c r="S19" s="8">
-        <v>0</v>
-      </c>
-      <c r="T19" s="8">
-        <v>0</v>
-      </c>
-      <c r="U19" s="8">
-        <v>0.000983796296296296</v>
-      </c>
-      <c r="V19" s="9">
-        <v>0</v>
-      </c>
-      <c r="W19" s="9">
-        <v>44.3</v>
-      </c>
-      <c r="X19" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="9">
-        <v>48.25</v>
-      </c>
-      <c r="AA19" s="9">
+      <c r="AA19" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="20" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E20" s="8">
-        <v>0.00127314814814815</v>
+        <v>0.00119212962962963</v>
       </c>
       <c r="F20" s="8">
-        <v>0.00128472222222222</v>
+        <v>0.00116898148148148</v>
       </c>
       <c r="G20" s="9">
-        <v>89.5510204081633</v>
+        <v>84.6530612244898</v>
       </c>
       <c r="H20" s="9">
-        <v>89.3877551020408</v>
+        <v>84.7959183673469</v>
       </c>
       <c r="I20" s="9">
-        <v>49</v>
+        <v>34.47</v>
       </c>
       <c r="J20" s="9">
-        <v>47.49</v>
+        <v>33.22</v>
       </c>
       <c r="K20" s="9">
         <v>49</v>
@@ -2124,11 +2130,11 @@
       <c r="M20" s="9">
         <v>49</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="O20" s="8">
         <v>1.15740740740741e-005</v>
-      </c>
-      <c r="O20" s="8">
-        <v>5.78703703703704e-005</v>
       </c>
       <c r="P20" s="8">
         <v>0.000185185185185185</v>
@@ -2137,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="R20" s="8">
-        <v>0.000185185185185185</v>
+        <v>0.000138888888888889</v>
       </c>
       <c r="S20" s="8">
         <v>0</v>
@@ -2152,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="9">
-        <v>46.16</v>
+        <v>36.44</v>
       </c>
       <c r="X20" s="9">
         <v>0</v>
@@ -2169,34 +2175,34 @@
     </row>
     <row r="21" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" s="8">
-        <v>0.0012962962962963</v>
+        <v>0.00138888888888889</v>
       </c>
       <c r="F21" s="8">
-        <v>0.00130787037037037</v>
+        <v>0.00138888888888889</v>
       </c>
       <c r="G21" s="9">
-        <v>88.6122448979592</v>
+        <v>82.6530612244898</v>
       </c>
       <c r="H21" s="9">
-        <v>88.4489795918367</v>
+        <v>82.6530612244898</v>
       </c>
       <c r="I21" s="9">
-        <v>47.52</v>
+        <v>41.48</v>
       </c>
       <c r="J21" s="9">
-        <v>46.96</v>
+        <v>41.48</v>
       </c>
       <c r="K21" s="9">
         <v>49</v>
@@ -2208,19 +2214,19 @@
         <v>49</v>
       </c>
       <c r="N21" s="8">
-        <v>1.15740740740741e-005</v>
+        <v>0</v>
       </c>
       <c r="O21" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0</v>
       </c>
       <c r="P21" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="8">
         <v>0</v>
       </c>
       <c r="R21" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="S21" s="8">
         <v>0</v>
@@ -2235,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="W21" s="9">
-        <v>45.61</v>
+        <v>0</v>
       </c>
       <c r="X21" s="9">
         <v>0</v>
@@ -2252,34 +2258,34 @@
     </row>
     <row r="22" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22" s="8">
-        <v>0.00123842592592593</v>
+        <v>0.0015625</v>
       </c>
       <c r="F22" s="8">
-        <v>0.00136574074074074</v>
+        <v>0.0015625</v>
       </c>
       <c r="G22" s="9">
-        <v>84.3265306122449</v>
+        <v>80.2244897959184</v>
       </c>
       <c r="H22" s="9">
-        <v>82.530612244898</v>
+        <v>80.2244897959184</v>
       </c>
       <c r="I22" s="9">
-        <v>36.78</v>
+        <v>46.23</v>
       </c>
       <c r="J22" s="9">
-        <v>36.74</v>
+        <v>46.23</v>
       </c>
       <c r="K22" s="9">
         <v>49</v>
@@ -2291,19 +2297,19 @@
         <v>49</v>
       </c>
       <c r="N22" s="8">
-        <v>0.000138888888888889</v>
+        <v>0</v>
       </c>
       <c r="O22" s="8">
-        <v>0.000219907407407407</v>
+        <v>0</v>
       </c>
       <c r="P22" s="8">
-        <v>0.000648148148148148</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="8">
         <v>0</v>
       </c>
       <c r="R22" s="8">
-        <v>0.000393518518518519</v>
+        <v>0</v>
       </c>
       <c r="S22" s="8">
         <v>0</v>
@@ -2318,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="9">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="X22" s="9">
         <v>0</v>
@@ -2335,16 +2341,16 @@
     </row>
     <row r="23" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8">
         <v>0.00163194444444444</v>
@@ -2418,34 +2424,34 @@
     </row>
     <row r="24" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E24" s="8">
-        <v>0.0015625</v>
+        <v>0.00123842592592593</v>
       </c>
       <c r="F24" s="8">
-        <v>0.0015625</v>
+        <v>0.00136574074074074</v>
       </c>
       <c r="G24" s="9">
-        <v>80.2244897959184</v>
+        <v>84.3265306122449</v>
       </c>
       <c r="H24" s="9">
-        <v>80.2244897959184</v>
+        <v>82.530612244898</v>
       </c>
       <c r="I24" s="9">
-        <v>46.23</v>
+        <v>36.78</v>
       </c>
       <c r="J24" s="9">
-        <v>46.23</v>
+        <v>36.74</v>
       </c>
       <c r="K24" s="9">
         <v>49</v>
@@ -2457,19 +2463,19 @@
         <v>49</v>
       </c>
       <c r="N24" s="8">
-        <v>0</v>
+        <v>0.000138888888888889</v>
       </c>
       <c r="O24" s="8">
-        <v>0</v>
+        <v>0.000219907407407407</v>
       </c>
       <c r="P24" s="8">
-        <v>0</v>
+        <v>0.000648148148148148</v>
       </c>
       <c r="Q24" s="8">
         <v>0</v>
       </c>
       <c r="R24" s="8">
-        <v>0</v>
+        <v>0.000393518518518519</v>
       </c>
       <c r="S24" s="8">
         <v>0</v>
@@ -2484,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="W24" s="9">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="X24" s="9">
         <v>0</v>
@@ -2501,34 +2507,34 @@
     </row>
     <row r="25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" s="8">
-        <v>0.00138888888888889</v>
+        <v>0.0012962962962963</v>
       </c>
       <c r="F25" s="8">
-        <v>0.00138888888888889</v>
+        <v>0.00130787037037037</v>
       </c>
       <c r="G25" s="9">
-        <v>82.6530612244898</v>
+        <v>88.6122448979592</v>
       </c>
       <c r="H25" s="9">
-        <v>82.6530612244898</v>
+        <v>88.4489795918367</v>
       </c>
       <c r="I25" s="9">
-        <v>41.48</v>
+        <v>47.52</v>
       </c>
       <c r="J25" s="9">
-        <v>41.48</v>
+        <v>46.96</v>
       </c>
       <c r="K25" s="9">
         <v>49</v>
@@ -2540,19 +2546,19 @@
         <v>49</v>
       </c>
       <c r="N25" s="8">
-        <v>0</v>
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="O25" s="8">
-        <v>0</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P25" s="8">
-        <v>0</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="Q25" s="8">
         <v>0</v>
       </c>
       <c r="R25" s="8">
-        <v>0</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="S25" s="8">
         <v>0</v>
@@ -2567,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="W25" s="9">
-        <v>0</v>
+        <v>45.61</v>
       </c>
       <c r="X25" s="9">
         <v>0</v>
@@ -2584,34 +2590,34 @@
     </row>
     <row r="26" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" s="8">
-        <v>0.00119212962962963</v>
+        <v>0.00127314814814815</v>
       </c>
       <c r="F26" s="8">
-        <v>0.00116898148148148</v>
+        <v>0.00128472222222222</v>
       </c>
       <c r="G26" s="9">
-        <v>84.6530612244898</v>
+        <v>89.5510204081633</v>
       </c>
       <c r="H26" s="9">
-        <v>84.7959183673469</v>
+        <v>89.3877551020408</v>
       </c>
       <c r="I26" s="9">
-        <v>34.47</v>
+        <v>49</v>
       </c>
       <c r="J26" s="9">
-        <v>33.22</v>
+        <v>47.49</v>
       </c>
       <c r="K26" s="9">
         <v>49</v>
@@ -2622,11 +2628,11 @@
       <c r="M26" s="9">
         <v>49</v>
       </c>
-      <c r="N26" s="10" t="s">
-        <v>40</v>
+      <c r="N26" s="8">
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="O26" s="8">
-        <v>1.15740740740741e-005</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P26" s="8">
         <v>0.000185185185185185</v>
@@ -2635,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="R26" s="8">
-        <v>0.000138888888888889</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="S26" s="8">
         <v>0</v>
@@ -2650,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="W26" s="9">
-        <v>36.44</v>
+        <v>46.16</v>
       </c>
       <c r="X26" s="9">
         <v>0</v>
@@ -2666,198 +2672,198 @@
       </c>
     </row>
     <row r="27" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>16</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0.00127314814814815</v>
-      </c>
-      <c r="F27" s="4">
-        <v>0.00133101851851852</v>
-      </c>
-      <c r="G27" s="5">
-        <v>87.2517006802721</v>
-      </c>
-      <c r="H27" s="5">
-        <v>86.6428571428571</v>
-      </c>
-      <c r="I27" s="5">
-        <v>265.63</v>
-      </c>
-      <c r="J27" s="5">
-        <v>269.25</v>
-      </c>
-      <c r="K27" s="5">
-        <v>294</v>
-      </c>
-      <c r="L27" s="5">
-        <v>294</v>
-      </c>
-      <c r="M27" s="5">
-        <v>294</v>
-      </c>
-      <c r="N27" s="4">
+      <c r="A27" s="6">
+        <v>19</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.00099537037037037</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0.00101851851851852</v>
+      </c>
+      <c r="G27" s="9">
+        <v>91.3673469387755</v>
+      </c>
+      <c r="H27" s="9">
+        <v>91.2448979591837</v>
+      </c>
+      <c r="I27" s="9">
+        <v>48.27</v>
+      </c>
+      <c r="J27" s="9">
+        <v>45.45</v>
+      </c>
+      <c r="K27" s="9">
+        <v>49</v>
+      </c>
+      <c r="L27" s="9">
+        <v>49</v>
+      </c>
+      <c r="M27" s="9">
+        <v>49</v>
+      </c>
+      <c r="N27" s="8">
+        <v>1.15740740740741e-005</v>
+      </c>
+      <c r="O27" s="8">
         <v>5.78703703703704e-005</v>
       </c>
-      <c r="O27" s="4">
-        <v>9.25925925925926e-005</v>
-      </c>
-      <c r="P27" s="4">
-        <v>0.000231481481481481</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>0</v>
-      </c>
-      <c r="R27" s="4">
+      <c r="P27" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
+        <v>0.000173611111111111</v>
+      </c>
+      <c r="S27" s="8">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8">
+        <v>0.000983796296296296</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0</v>
+      </c>
+      <c r="W27" s="9">
+        <v>44.3</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>48.25</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>18</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0.00130787037037037</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0.00134259259259259</v>
+      </c>
+      <c r="G28" s="5">
+        <v>86.7026239067055</v>
+      </c>
+      <c r="H28" s="5">
+        <v>86.2507288629738</v>
+      </c>
+      <c r="I28" s="5">
+        <v>312.44</v>
+      </c>
+      <c r="J28" s="5">
+        <v>314.64</v>
+      </c>
+      <c r="K28" s="5">
+        <v>343</v>
+      </c>
+      <c r="L28" s="5">
+        <v>343</v>
+      </c>
+      <c r="M28" s="5">
+        <v>343</v>
+      </c>
+      <c r="N28" s="4">
+        <v>4.62962962962963e-005</v>
+      </c>
+      <c r="O28" s="4">
+        <v>8.10185185185185e-005</v>
+      </c>
+      <c r="P28" s="4">
+        <v>0.000219907407407407</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>0</v>
+      </c>
+      <c r="R28" s="4">
         <v>0.000196759259259259</v>
       </c>
-      <c r="S27" s="4">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4">
-        <v>0.000173611111111111</v>
-      </c>
-      <c r="V27" s="5">
-        <v>0</v>
-      </c>
-      <c r="W27" s="5">
-        <v>215.04</v>
-      </c>
-      <c r="X27" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="5">
+      <c r="S28" s="4">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="V28" s="5">
+        <v>0</v>
+      </c>
+      <c r="W28" s="5">
+        <v>259.83</v>
+      </c>
+      <c r="X28" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
         <v>48.26</v>
       </c>
-      <c r="AA27" s="5">
+      <c r="AA28" s="5">
         <v>3.4</v>
-      </c>
-    </row>
-    <row r="28" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>15</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.00103009259259259</v>
-      </c>
-      <c r="F28" s="8">
-        <v>0.00104166666666667</v>
-      </c>
-      <c r="G28" s="9">
-        <v>90.9183673469388</v>
-      </c>
-      <c r="H28" s="9">
-        <v>91.0816326530612</v>
-      </c>
-      <c r="I28" s="9">
-        <v>48.28</v>
-      </c>
-      <c r="J28" s="9">
-        <v>45.51</v>
-      </c>
-      <c r="K28" s="9">
-        <v>49</v>
-      </c>
-      <c r="L28" s="9">
-        <v>49</v>
-      </c>
-      <c r="M28" s="9">
-        <v>49</v>
-      </c>
-      <c r="N28" s="8">
-        <v>1.15740740740741e-005</v>
-      </c>
-      <c r="O28" s="8">
-        <v>5.78703703703704e-005</v>
-      </c>
-      <c r="P28" s="8">
-        <v>0.000185185185185185</v>
-      </c>
-      <c r="Q28" s="8">
-        <v>0</v>
-      </c>
-      <c r="R28" s="8">
-        <v>0.000173611111111111</v>
-      </c>
-      <c r="S28" s="8">
-        <v>0</v>
-      </c>
-      <c r="T28" s="8">
-        <v>0</v>
-      </c>
-      <c r="U28" s="8">
-        <v>0.00101851851851852</v>
-      </c>
-      <c r="V28" s="9">
-        <v>0</v>
-      </c>
-      <c r="W28" s="9">
-        <v>44.24</v>
-      </c>
-      <c r="X28" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="9">
-        <v>48.26</v>
-      </c>
-      <c r="AA28" s="9">
-        <v>0</v>
       </c>
     </row>
     <row r="29" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E29" s="8">
-        <v>0.00125</v>
+        <v>0.00149305555555556</v>
       </c>
       <c r="F29" s="8">
-        <v>0.00126157407407407</v>
+        <v>0.00144675925925926</v>
       </c>
       <c r="G29" s="9">
-        <v>89.4489795918367</v>
+        <v>83.4081632653061</v>
       </c>
       <c r="H29" s="9">
-        <v>89.2448979591837</v>
+        <v>83.8979591836735</v>
       </c>
       <c r="I29" s="9">
-        <v>47.82</v>
+        <v>46.81</v>
       </c>
       <c r="J29" s="9">
-        <v>47.49</v>
+        <v>45.39</v>
       </c>
       <c r="K29" s="9">
         <v>49</v>
@@ -2868,11 +2874,11 @@
       <c r="M29" s="9">
         <v>49</v>
       </c>
-      <c r="N29" s="8">
-        <v>1.15740740740741e-005</v>
+      <c r="N29" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="O29" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0</v>
       </c>
       <c r="P29" s="8">
         <v>0.000185185185185185</v>
@@ -2896,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="W29" s="9">
-        <v>46.13</v>
+        <v>44.79</v>
       </c>
       <c r="X29" s="9">
         <v>0</v>
@@ -2913,34 +2919,34 @@
     </row>
     <row r="30" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" s="8">
-        <v>0.00128472222222222</v>
+        <v>0.00158564814814815</v>
       </c>
       <c r="F30" s="8">
-        <v>0.0012962962962963</v>
+        <v>0.00158564814814815</v>
       </c>
       <c r="G30" s="9">
-        <v>88.6938775510204</v>
+        <v>81.7755102040816</v>
       </c>
       <c r="H30" s="9">
-        <v>88.4489795918367</v>
+        <v>81.7755102040816</v>
       </c>
       <c r="I30" s="9">
-        <v>47.04</v>
+        <v>47.01</v>
       </c>
       <c r="J30" s="9">
-        <v>46.35</v>
+        <v>47.01</v>
       </c>
       <c r="K30" s="9">
         <v>49</v>
@@ -2952,19 +2958,19 @@
         <v>49</v>
       </c>
       <c r="N30" s="8">
-        <v>1.15740740740741e-005</v>
+        <v>0</v>
       </c>
       <c r="O30" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>0</v>
       </c>
       <c r="P30" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="8">
         <v>0</v>
       </c>
       <c r="R30" s="8">
-        <v>0.000185185185185185</v>
+        <v>0</v>
       </c>
       <c r="S30" s="8">
         <v>0</v>
@@ -2979,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="9">
-        <v>45.07</v>
+        <v>0</v>
       </c>
       <c r="X30" s="9">
         <v>0</v>
@@ -2996,34 +3002,34 @@
     </row>
     <row r="31" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" s="8">
-        <v>0.00103009259259259</v>
+        <v>0.00145833333333333</v>
       </c>
       <c r="F31" s="8">
-        <v>0.00119212962962963</v>
+        <v>0.00158564814814815</v>
       </c>
       <c r="G31" s="9">
-        <v>89.0612244897959</v>
+        <v>83.6122448979592</v>
       </c>
       <c r="H31" s="9">
-        <v>87.530612244898</v>
+        <v>81.7755102040816</v>
       </c>
       <c r="I31" s="9">
-        <v>33.16</v>
+        <v>42.32</v>
       </c>
       <c r="J31" s="9">
-        <v>35.88</v>
+        <v>47.01</v>
       </c>
       <c r="K31" s="9">
         <v>49</v>
@@ -3035,19 +3041,19 @@
         <v>49</v>
       </c>
       <c r="N31" s="8">
-        <v>0.000185185185185185</v>
+        <v>0.000127314814814815</v>
       </c>
       <c r="O31" s="8">
-        <v>0.000243055555555556</v>
+        <v>0.000138888888888889</v>
       </c>
       <c r="P31" s="8">
-        <v>0.000648148148148148</v>
+        <v>0.000150462962962963</v>
       </c>
       <c r="Q31" s="8">
         <v>0</v>
       </c>
       <c r="R31" s="8">
-        <v>0.00037037037037037</v>
+        <v>0.00025462962962963</v>
       </c>
       <c r="S31" s="8">
         <v>0</v>
@@ -3062,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="W31" s="9">
-        <v>33.22</v>
+        <v>46.38</v>
       </c>
       <c r="X31" s="9">
         <v>0</v>
@@ -3074,39 +3080,39 @@
         <v>0</v>
       </c>
       <c r="AA31" s="9">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E32" s="8">
-        <v>0.00145833333333333</v>
+        <v>0.00103009259259259</v>
       </c>
       <c r="F32" s="8">
-        <v>0.00158564814814815</v>
+        <v>0.00119212962962963</v>
       </c>
       <c r="G32" s="9">
-        <v>83.6122448979592</v>
+        <v>89.0612244897959</v>
       </c>
       <c r="H32" s="9">
-        <v>81.7755102040816</v>
+        <v>87.530612244898</v>
       </c>
       <c r="I32" s="9">
-        <v>42.32</v>
+        <v>33.16</v>
       </c>
       <c r="J32" s="9">
-        <v>47.01</v>
+        <v>35.88</v>
       </c>
       <c r="K32" s="9">
         <v>49</v>
@@ -3118,19 +3124,19 @@
         <v>49</v>
       </c>
       <c r="N32" s="8">
-        <v>0.000127314814814815</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="O32" s="8">
-        <v>0.000138888888888889</v>
+        <v>0.000243055555555556</v>
       </c>
       <c r="P32" s="8">
-        <v>0.000150462962962963</v>
+        <v>0.000648148148148148</v>
       </c>
       <c r="Q32" s="8">
         <v>0</v>
       </c>
       <c r="R32" s="8">
-        <v>0.00025462962962963</v>
+        <v>0.00037037037037037</v>
       </c>
       <c r="S32" s="8">
         <v>0</v>
@@ -3145,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="W32" s="9">
-        <v>46.38</v>
+        <v>33.22</v>
       </c>
       <c r="X32" s="9">
         <v>0</v>
@@ -3157,175 +3163,178 @@
         <v>0</v>
       </c>
       <c r="AA32" s="9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.00128472222222222</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0.0012962962962963</v>
+      </c>
+      <c r="G33" s="9">
+        <v>88.6938775510204</v>
+      </c>
+      <c r="H33" s="9">
+        <v>88.4489795918367</v>
+      </c>
+      <c r="I33" s="9">
+        <v>47.04</v>
+      </c>
+      <c r="J33" s="9">
+        <v>46.35</v>
+      </c>
+      <c r="K33" s="9">
+        <v>49</v>
+      </c>
+      <c r="L33" s="9">
+        <v>49</v>
+      </c>
+      <c r="M33" s="9">
+        <v>49</v>
+      </c>
+      <c r="N33" s="8">
+        <v>1.15740740740741e-005</v>
+      </c>
+      <c r="O33" s="8">
+        <v>5.78703703703704e-005</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="S33" s="8">
+        <v>0</v>
+      </c>
+      <c r="T33" s="8">
+        <v>0</v>
+      </c>
+      <c r="U33" s="8">
+        <v>0</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0</v>
+      </c>
+      <c r="W33" s="9">
+        <v>45.07</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>12</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="8">
-        <v>0.00158564814814815</v>
-      </c>
-      <c r="F33" s="8">
-        <v>0.00158564814814815</v>
-      </c>
-      <c r="G33" s="9">
-        <v>81.7755102040816</v>
-      </c>
-      <c r="H33" s="9">
-        <v>81.7755102040816</v>
-      </c>
-      <c r="I33" s="9">
-        <v>47.01</v>
-      </c>
-      <c r="J33" s="9">
-        <v>47.01</v>
-      </c>
-      <c r="K33" s="9">
-        <v>49</v>
-      </c>
-      <c r="L33" s="9">
-        <v>49</v>
-      </c>
-      <c r="M33" s="9">
-        <v>49</v>
-      </c>
-      <c r="N33" s="8">
-        <v>0</v>
-      </c>
-      <c r="O33" s="8">
-        <v>0</v>
-      </c>
-      <c r="P33" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>0</v>
-      </c>
-      <c r="R33" s="8">
-        <v>0</v>
-      </c>
-      <c r="S33" s="8">
-        <v>0</v>
-      </c>
-      <c r="T33" s="8">
-        <v>0</v>
-      </c>
-      <c r="U33" s="8">
-        <v>0</v>
-      </c>
-      <c r="V33" s="9">
-        <v>0</v>
-      </c>
-      <c r="W33" s="9">
-        <v>0</v>
-      </c>
-      <c r="X33" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>9</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0.00142361111111111</v>
-      </c>
-      <c r="F34" s="4">
-        <v>0.00146990740740741</v>
-      </c>
-      <c r="G34" s="5">
-        <v>84.152332361516</v>
-      </c>
-      <c r="H34" s="5">
-        <v>83.6144314868805</v>
-      </c>
-      <c r="I34" s="5">
-        <v>1235.55</v>
-      </c>
-      <c r="J34" s="5">
-        <v>1223.74</v>
-      </c>
-      <c r="K34" s="5">
-        <v>1372</v>
-      </c>
-      <c r="L34" s="5">
-        <v>1372</v>
-      </c>
-      <c r="M34" s="5">
-        <v>1372</v>
-      </c>
-      <c r="N34" s="4">
-        <v>4.62962962962963e-005</v>
-      </c>
-      <c r="O34" s="4">
-        <v>8.10185185185185e-005</v>
-      </c>
-      <c r="P34" s="4">
-        <v>0.000208333333333333</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>0</v>
-      </c>
-      <c r="R34" s="4">
-        <v>0.000173611111111111</v>
-      </c>
-      <c r="S34" s="4">
-        <v>0</v>
-      </c>
-      <c r="T34" s="4">
-        <v>0</v>
-      </c>
-      <c r="U34" s="4">
-        <v>0.000104166666666667</v>
-      </c>
-      <c r="V34" s="5">
-        <v>0</v>
-      </c>
-      <c r="W34" s="5">
-        <v>932.76</v>
-      </c>
-      <c r="X34" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="5">
-        <v>144.71</v>
-      </c>
-      <c r="AA34" s="5">
-        <v>8.08</v>
+      <c r="E34" s="8">
+        <v>0.00125</v>
+      </c>
+      <c r="F34" s="8">
+        <v>0.00126157407407407</v>
+      </c>
+      <c r="G34" s="9">
+        <v>89.4489795918367</v>
+      </c>
+      <c r="H34" s="9">
+        <v>89.2448979591837</v>
+      </c>
+      <c r="I34" s="9">
+        <v>47.82</v>
+      </c>
+      <c r="J34" s="9">
+        <v>47.49</v>
+      </c>
+      <c r="K34" s="9">
+        <v>49</v>
+      </c>
+      <c r="L34" s="9">
+        <v>49</v>
+      </c>
+      <c r="M34" s="9">
+        <v>49</v>
+      </c>
+      <c r="N34" s="8">
+        <v>1.15740740740741e-005</v>
+      </c>
+      <c r="O34" s="8">
+        <v>5.78703703703704e-005</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0</v>
+      </c>
+      <c r="R34" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="S34" s="8">
+        <v>0</v>
+      </c>
+      <c r="T34" s="8">
+        <v>0</v>
+      </c>
+      <c r="U34" s="8">
+        <v>0</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>46.13</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="35" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>27</v>
@@ -3334,40 +3343,40 @@
         <v>42</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E35" s="8">
-        <v>0.00142361111111111</v>
+        <v>0.00103009259259259</v>
       </c>
       <c r="F35" s="8">
-        <v>0.00141203703703704</v>
+        <v>0.00104166666666667</v>
       </c>
       <c r="G35" s="9">
-        <v>83.8928571428571</v>
+        <v>90.9183673469388</v>
       </c>
       <c r="H35" s="9">
-        <v>84.1326530612245</v>
+        <v>91.0816326530612</v>
       </c>
       <c r="I35" s="9">
-        <v>185.69</v>
+        <v>48.28</v>
       </c>
       <c r="J35" s="9">
-        <v>177.69</v>
+        <v>45.51</v>
       </c>
       <c r="K35" s="9">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="L35" s="9">
-        <v>196</v>
+        <v>49</v>
       </c>
       <c r="M35" s="9">
-        <v>196</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="N35" s="8">
+        <v>1.15740740740741e-005</v>
       </c>
       <c r="O35" s="8">
-        <v>3.47222222222222e-005</v>
+        <v>5.78703703703704e-005</v>
       </c>
       <c r="P35" s="8">
         <v>0.000185185185185185</v>
@@ -3385,13 +3394,13 @@
         <v>0</v>
       </c>
       <c r="U35" s="8">
-        <v>0.000497685185185185</v>
+        <v>0.00101851851851852</v>
       </c>
       <c r="V35" s="9">
         <v>0</v>
       </c>
       <c r="W35" s="9">
-        <v>175.68</v>
+        <v>44.24</v>
       </c>
       <c r="X35" s="9">
         <v>0</v>
@@ -3400,140 +3409,137 @@
         <v>0</v>
       </c>
       <c r="Z35" s="9">
-        <v>96.51</v>
+        <v>48.26</v>
       </c>
       <c r="AA35" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="36" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>7</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.00157407407407407</v>
-      </c>
-      <c r="F36" s="8">
-        <v>0.00158564814814815</v>
-      </c>
-      <c r="G36" s="9">
-        <v>82.5714285714286</v>
-      </c>
-      <c r="H36" s="9">
-        <v>82.4030612244898</v>
-      </c>
-      <c r="I36" s="9">
-        <v>186.19</v>
-      </c>
-      <c r="J36" s="9">
-        <v>184.6</v>
-      </c>
-      <c r="K36" s="9">
-        <v>196</v>
-      </c>
-      <c r="L36" s="9">
-        <v>196</v>
-      </c>
-      <c r="M36" s="9">
-        <v>196</v>
-      </c>
-      <c r="N36" s="8">
-        <v>1.15740740740741e-005</v>
-      </c>
-      <c r="O36" s="8">
-        <v>5.78703703703704e-005</v>
-      </c>
-      <c r="P36" s="8">
-        <v>0.000185185185185185</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>0</v>
-      </c>
-      <c r="R36" s="8">
-        <v>0.000185185185185185</v>
-      </c>
-      <c r="S36" s="8">
-        <v>0</v>
-      </c>
-      <c r="T36" s="8">
-        <v>0</v>
-      </c>
-      <c r="U36" s="8">
-        <v>0</v>
-      </c>
-      <c r="V36" s="9">
-        <v>0</v>
-      </c>
-      <c r="W36" s="9">
-        <v>179.46</v>
-      </c>
-      <c r="X36" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="9">
-        <v>0</v>
+      <c r="A36" s="2">
+        <v>10</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0.00143518518518519</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0.00145833333333333</v>
+      </c>
+      <c r="G36" s="5">
+        <v>84.1700680272109</v>
+      </c>
+      <c r="H36" s="5">
+        <v>83.6795918367347</v>
+      </c>
+      <c r="I36" s="5">
+        <v>1330.72</v>
+      </c>
+      <c r="J36" s="5">
+        <v>1315.17</v>
+      </c>
+      <c r="K36" s="5">
+        <v>1470</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1470</v>
+      </c>
+      <c r="M36" s="5">
+        <v>1470</v>
+      </c>
+      <c r="N36" s="4">
+        <v>3.47222222222222e-005</v>
+      </c>
+      <c r="O36" s="4">
+        <v>8.10185185185185e-005</v>
+      </c>
+      <c r="P36" s="4">
+        <v>0.000208333333333333</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0</v>
+      </c>
+      <c r="R36" s="4">
+        <v>0.000173611111111111</v>
+      </c>
+      <c r="S36" s="4">
+        <v>0</v>
+      </c>
+      <c r="T36" s="4">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="V36" s="5">
+        <v>0</v>
+      </c>
+      <c r="W36" s="5">
+        <v>1022.3</v>
+      </c>
+      <c r="X36" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <v>193.03</v>
+      </c>
+      <c r="AA36" s="5">
+        <v>8.08</v>
       </c>
     </row>
     <row r="37" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E37" s="8">
-        <v>0.00150462962962963</v>
+        <v>0.00146990740740741</v>
       </c>
       <c r="F37" s="8">
-        <v>0.0015162037037037</v>
+        <v>0.00145833333333333</v>
       </c>
       <c r="G37" s="9">
-        <v>83.7448979591837</v>
+        <v>84.4183673469388</v>
       </c>
       <c r="H37" s="9">
-        <v>83.4948979591837</v>
+        <v>84.5918367346939</v>
       </c>
       <c r="I37" s="9">
-        <v>192.56</v>
+        <v>95.17</v>
       </c>
       <c r="J37" s="9">
-        <v>178.43</v>
+        <v>91.43</v>
       </c>
       <c r="K37" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="L37" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="M37" s="9">
-        <v>196</v>
-      </c>
-      <c r="N37" s="8">
-        <v>1.15740740740741e-005</v>
+        <v>98</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="O37" s="8">
-        <v>5.78703703703704e-005</v>
+        <v>3.47222222222222e-005</v>
       </c>
       <c r="P37" s="8">
         <v>0.000185185185185185</v>
@@ -3542,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="R37" s="8">
-        <v>0.000173611111111111</v>
+        <v>0.000185185185185185</v>
       </c>
       <c r="S37" s="8">
         <v>0</v>
@@ -3551,13 +3557,13 @@
         <v>0</v>
       </c>
       <c r="U37" s="8">
-        <v>0</v>
+        <v>0.000717592592592593</v>
       </c>
       <c r="V37" s="9">
         <v>0</v>
       </c>
       <c r="W37" s="9">
-        <v>173.76</v>
+        <v>89.54</v>
       </c>
       <c r="X37" s="9">
         <v>0</v>
@@ -3566,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="9">
-        <v>0</v>
+        <v>48.32</v>
       </c>
       <c r="AA37" s="9">
         <v>0</v>
@@ -3574,59 +3580,59 @@
     </row>
     <row r="38" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E38" s="8">
-        <v>0.00127314814814815</v>
+        <v>0.00108796296296296</v>
       </c>
       <c r="F38" s="8">
-        <v>0.00138888888888889</v>
+        <v>0.00108796296296296</v>
       </c>
       <c r="G38" s="9">
-        <v>84.8418367346939</v>
+        <v>88.530612244898</v>
       </c>
       <c r="H38" s="9">
-        <v>83.4591836734694</v>
+        <v>88.5612244897959</v>
       </c>
       <c r="I38" s="9">
-        <v>132.3</v>
+        <v>82.7</v>
       </c>
       <c r="J38" s="9">
-        <v>139.48</v>
+        <v>78.73</v>
       </c>
       <c r="K38" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="L38" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="M38" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="N38" s="8">
+        <v>0</v>
+      </c>
+      <c r="O38" s="8">
+        <v>3.47222222222222e-005</v>
+      </c>
+      <c r="P38" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>0</v>
+      </c>
+      <c r="R38" s="8">
         <v>0.000162037037037037</v>
       </c>
-      <c r="O38" s="8">
-        <v>0.000243055555555556</v>
-      </c>
-      <c r="P38" s="8">
-        <v>0.000648148148148148</v>
-      </c>
-      <c r="Q38" s="8">
-        <v>0</v>
-      </c>
-      <c r="R38" s="8">
-        <v>0.000381944444444444</v>
-      </c>
       <c r="S38" s="8">
         <v>0</v>
       </c>
@@ -3634,13 +3640,13 @@
         <v>0</v>
       </c>
       <c r="U38" s="8">
-        <v>0</v>
+        <v>0.000486111111111111</v>
       </c>
       <c r="V38" s="9">
         <v>0</v>
       </c>
       <c r="W38" s="9">
-        <v>133.56</v>
+        <v>80.76</v>
       </c>
       <c r="X38" s="9">
         <v>0</v>
@@ -3649,66 +3655,66 @@
         <v>0</v>
       </c>
       <c r="Z38" s="9">
-        <v>0</v>
+        <v>48.2</v>
       </c>
       <c r="AA38" s="9">
-        <v>8.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E39" s="8">
-        <v>0.00171296296296296</v>
+        <v>0.00119212962962963</v>
       </c>
       <c r="F39" s="8">
-        <v>0.00184027777777778</v>
+        <v>0.00119212962962963</v>
       </c>
       <c r="G39" s="9">
-        <v>80.9948979591837</v>
+        <v>87.4897959183673</v>
       </c>
       <c r="H39" s="9">
-        <v>78.9285714285714</v>
+        <v>87.4897959183673</v>
       </c>
       <c r="I39" s="9">
-        <v>183.58</v>
+        <v>87</v>
       </c>
       <c r="J39" s="9">
-        <v>192.28</v>
+        <v>87</v>
       </c>
       <c r="K39" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="L39" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="M39" s="9">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="N39" s="8">
-        <v>0.000127314814814815</v>
+        <v>0</v>
       </c>
       <c r="O39" s="8">
-        <v>0.000138888888888889</v>
+        <v>0</v>
       </c>
       <c r="P39" s="8">
-        <v>0.000150462962962963</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="8">
         <v>0</v>
       </c>
       <c r="R39" s="8">
-        <v>0.000266203703703704</v>
+        <v>0</v>
       </c>
       <c r="S39" s="8">
         <v>0</v>
@@ -3723,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="9">
-        <v>189.54</v>
+        <v>0</v>
       </c>
       <c r="X39" s="9">
         <v>0</v>
@@ -3740,16 +3746,16 @@
     </row>
     <row r="40" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E40" s="8">
         <v>0.00137731481481481</v>
@@ -3823,58 +3829,58 @@
     </row>
     <row r="41" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E41" s="8">
-        <v>0.00119212962962963</v>
+        <v>0.00171296296296296</v>
       </c>
       <c r="F41" s="8">
-        <v>0.00119212962962963</v>
+        <v>0.00184027777777778</v>
       </c>
       <c r="G41" s="9">
-        <v>87.4897959183673</v>
+        <v>80.9948979591837</v>
       </c>
       <c r="H41" s="9">
-        <v>87.4897959183673</v>
+        <v>78.9285714285714</v>
       </c>
       <c r="I41" s="9">
-        <v>87</v>
+        <v>183.58</v>
       </c>
       <c r="J41" s="9">
-        <v>87</v>
+        <v>192.28</v>
       </c>
       <c r="K41" s="9">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="L41" s="9">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="M41" s="9">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="N41" s="8">
-        <v>0</v>
+        <v>0.000127314814814815</v>
       </c>
       <c r="O41" s="8">
-        <v>0</v>
+        <v>0.000138888888888889</v>
       </c>
       <c r="P41" s="8">
-        <v>0</v>
+        <v>0.000150462962962963</v>
       </c>
       <c r="Q41" s="8">
         <v>0</v>
       </c>
       <c r="R41" s="8">
-        <v>0</v>
+        <v>0.000266203703703704</v>
       </c>
       <c r="S41" s="8">
         <v>0</v>
@@ -3889,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="W41" s="9">
-        <v>0</v>
+        <v>189.54</v>
       </c>
       <c r="X41" s="9">
         <v>0</v>
@@ -3906,84 +3912,333 @@
     </row>
     <row r="42" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
+        <v>4</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.00127314814814815</v>
+      </c>
+      <c r="F42" s="8">
+        <v>0.00138888888888889</v>
+      </c>
+      <c r="G42" s="9">
+        <v>84.8418367346939</v>
+      </c>
+      <c r="H42" s="9">
+        <v>83.4591836734694</v>
+      </c>
+      <c r="I42" s="9">
+        <v>132.3</v>
+      </c>
+      <c r="J42" s="9">
+        <v>139.48</v>
+      </c>
+      <c r="K42" s="9">
+        <v>196</v>
+      </c>
+      <c r="L42" s="9">
+        <v>196</v>
+      </c>
+      <c r="M42" s="9">
+        <v>196</v>
+      </c>
+      <c r="N42" s="8">
+        <v>0.000162037037037037</v>
+      </c>
+      <c r="O42" s="8">
+        <v>0.000243055555555556</v>
+      </c>
+      <c r="P42" s="8">
+        <v>0.000648148148148148</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>0</v>
+      </c>
+      <c r="R42" s="8">
+        <v>0.000381944444444444</v>
+      </c>
+      <c r="S42" s="8">
+        <v>0</v>
+      </c>
+      <c r="T42" s="8">
+        <v>0</v>
+      </c>
+      <c r="U42" s="8">
+        <v>0</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>133.56</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="43" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>3</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.00150462962962963</v>
+      </c>
+      <c r="F43" s="8">
+        <v>0.0015162037037037</v>
+      </c>
+      <c r="G43" s="9">
+        <v>83.7448979591837</v>
+      </c>
+      <c r="H43" s="9">
+        <v>83.4948979591837</v>
+      </c>
+      <c r="I43" s="9">
+        <v>192.56</v>
+      </c>
+      <c r="J43" s="9">
+        <v>178.43</v>
+      </c>
+      <c r="K43" s="9">
+        <v>196</v>
+      </c>
+      <c r="L43" s="9">
+        <v>196</v>
+      </c>
+      <c r="M43" s="9">
+        <v>196</v>
+      </c>
+      <c r="N43" s="8">
+        <v>1.15740740740741e-005</v>
+      </c>
+      <c r="O43" s="8">
+        <v>5.78703703703704e-005</v>
+      </c>
+      <c r="P43" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>0</v>
+      </c>
+      <c r="R43" s="8">
+        <v>0.000173611111111111</v>
+      </c>
+      <c r="S43" s="8">
+        <v>0</v>
+      </c>
+      <c r="T43" s="8">
+        <v>0</v>
+      </c>
+      <c r="U43" s="8">
+        <v>0</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0</v>
+      </c>
+      <c r="W43" s="9">
+        <v>173.76</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>2</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.00157407407407407</v>
+      </c>
+      <c r="F44" s="8">
+        <v>0.00158564814814815</v>
+      </c>
+      <c r="G44" s="9">
+        <v>82.5714285714286</v>
+      </c>
+      <c r="H44" s="9">
+        <v>82.4030612244898</v>
+      </c>
+      <c r="I44" s="9">
+        <v>186.19</v>
+      </c>
+      <c r="J44" s="9">
+        <v>184.6</v>
+      </c>
+      <c r="K44" s="9">
+        <v>196</v>
+      </c>
+      <c r="L44" s="9">
+        <v>196</v>
+      </c>
+      <c r="M44" s="9">
+        <v>196</v>
+      </c>
+      <c r="N44" s="8">
+        <v>1.15740740740741e-005</v>
+      </c>
+      <c r="O44" s="8">
+        <v>5.78703703703704e-005</v>
+      </c>
+      <c r="P44" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>0</v>
+      </c>
+      <c r="R44" s="8">
+        <v>0.000185185185185185</v>
+      </c>
+      <c r="S44" s="8">
+        <v>0</v>
+      </c>
+      <c r="T44" s="8">
+        <v>0</v>
+      </c>
+      <c r="U44" s="8">
+        <v>0</v>
+      </c>
+      <c r="V44" s="9">
+        <v>0</v>
+      </c>
+      <c r="W44" s="9">
+        <v>179.46</v>
+      </c>
+      <c r="X44" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
         <v>1</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.00108796296296296</v>
-      </c>
-      <c r="F42" s="8">
-        <v>0.00108796296296296</v>
-      </c>
-      <c r="G42" s="9">
-        <v>88.530612244898</v>
-      </c>
-      <c r="H42" s="9">
-        <v>88.5612244897959</v>
-      </c>
-      <c r="I42" s="9">
-        <v>82.7</v>
-      </c>
-      <c r="J42" s="9">
-        <v>78.73</v>
-      </c>
-      <c r="K42" s="9">
-        <v>98</v>
-      </c>
-      <c r="L42" s="9">
-        <v>98</v>
-      </c>
-      <c r="M42" s="9">
-        <v>98</v>
-      </c>
-      <c r="N42" s="8">
-        <v>0</v>
-      </c>
-      <c r="O42" s="8">
+      <c r="B45" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.00142361111111111</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0.00141203703703704</v>
+      </c>
+      <c r="G45" s="9">
+        <v>83.8928571428571</v>
+      </c>
+      <c r="H45" s="9">
+        <v>84.1326530612245</v>
+      </c>
+      <c r="I45" s="9">
+        <v>185.69</v>
+      </c>
+      <c r="J45" s="9">
+        <v>177.69</v>
+      </c>
+      <c r="K45" s="9">
+        <v>196</v>
+      </c>
+      <c r="L45" s="9">
+        <v>196</v>
+      </c>
+      <c r="M45" s="9">
+        <v>196</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" s="8">
         <v>3.47222222222222e-005</v>
       </c>
-      <c r="P42" s="8">
+      <c r="P45" s="8">
         <v>0.000185185185185185</v>
       </c>
-      <c r="Q42" s="8">
-        <v>0</v>
-      </c>
-      <c r="R42" s="8">
-        <v>0.000162037037037037</v>
-      </c>
-      <c r="S42" s="8">
-        <v>0</v>
-      </c>
-      <c r="T42" s="8">
-        <v>0</v>
-      </c>
-      <c r="U42" s="8">
-        <v>0.000486111111111111</v>
-      </c>
-      <c r="V42" s="9">
-        <v>0</v>
-      </c>
-      <c r="W42" s="9">
-        <v>80.76</v>
-      </c>
-      <c r="X42" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="9">
-        <v>48.2</v>
-      </c>
-      <c r="AA42" s="9">
+      <c r="Q45" s="8">
+        <v>0</v>
+      </c>
+      <c r="R45" s="8">
+        <v>0.000173611111111111</v>
+      </c>
+      <c r="S45" s="8">
+        <v>0</v>
+      </c>
+      <c r="T45" s="8">
+        <v>0</v>
+      </c>
+      <c r="U45" s="8">
+        <v>0.000497685185185185</v>
+      </c>
+      <c r="V45" s="9">
+        <v>0</v>
+      </c>
+      <c r="W45" s="9">
+        <v>175.68</v>
+      </c>
+      <c r="X45" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="9">
+        <v>96.51</v>
+      </c>
+      <c r="AA45" s="9">
         <v>0</v>
       </c>
     </row>
